--- a/Template_HRC.xlsx
+++ b/Template_HRC.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:I72"/>
+  <dimension ref="C2:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -455,7 +455,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PK003702815749</t>
+          <t>PK003702736775</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1047007084.72</v>
+        <v>1188746128.64</v>
       </c>
     </row>
     <row r="8">
@@ -511,48 +511,48 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-37.71999996528029</v>
+        <v>-141739081.6399999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Referencia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Método de Pago</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>Referencia</t>
+          <t>PK003702736775</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>8/11/25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Método de Pago</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PK003702815749</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8/11/25</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>1047007047</v>
       </c>
     </row>
@@ -601,16 +601,16 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>PMP1243434</t>
+          <t>PMP1249244</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>165989699</v>
+        <v>31277975</v>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="2" t="n">
-        <v>165989699</v>
+        <v>31277975</v>
       </c>
       <c r="I19" s="7" t="inlineStr"/>
     </row>
@@ -622,16 +622,16 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>PMP1243435</t>
+          <t>PMP1249258</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>29856410</v>
+        <v>1102345</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="2" t="n">
-        <v>29856410</v>
+        <v>1102345</v>
       </c>
       <c r="I20" s="7" t="inlineStr"/>
     </row>
@@ -643,16 +643,16 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>PMP1243436</t>
+          <t>PMP1249400</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12528130</v>
+        <v>27692682</v>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="2" t="n">
-        <v>12528130</v>
+        <v>27692682</v>
       </c>
       <c r="I21" s="7" t="inlineStr"/>
     </row>
@@ -664,16 +664,16 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>PMP1243437</t>
+          <t>PMP1249405</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>83124</v>
+        <v>4992313</v>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="2" t="n">
-        <v>83124</v>
+        <v>4992313</v>
       </c>
       <c r="I22" s="7" t="inlineStr"/>
     </row>
@@ -685,16 +685,16 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>PMP1243438</t>
+          <t>PMP1249557</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>53514044</v>
+        <v>20100423</v>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="2" t="n">
-        <v>53514044</v>
+        <v>20100423</v>
       </c>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
@@ -706,16 +706,16 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>PMP1243439</t>
+          <t>PMP1249558</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>757032037</v>
+        <v>72307698</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="2" t="n">
-        <v>757032037</v>
+        <v>72307698</v>
       </c>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
@@ -727,16 +727,16 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>PMP1243546</t>
+          <t>PMP1249559</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>122759901</v>
+        <v>94379986</v>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="2" t="n">
-        <v>122759901</v>
+        <v>94379986</v>
       </c>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
@@ -748,16 +748,16 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>PMP1243587</t>
+          <t>PMP1249560</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132622525</v>
+        <v>2263380</v>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="2" t="n">
-        <v>132622525</v>
+        <v>2263380</v>
       </c>
       <c r="I26" s="7" t="inlineStr"/>
     </row>
@@ -769,645 +769,417 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>PMP1243639</t>
+          <t>PMP1249561</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>343873745</v>
+        <v>79954317</v>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="2" t="n">
-        <v>343873745</v>
+        <v>79954317</v>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>0085489002</t>
+          <t>PMP1249562</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-106616</v>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>19480076</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="2" t="n">
-        <v>-106616</v>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489002</t>
-        </is>
-      </c>
+        <v>19480076</v>
+      </c>
+      <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>0085489003</t>
+          <t>PMP1249563</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-280732</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>122200697</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
       <c r="H29" s="2" t="n">
-        <v>-280732</v>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489003</t>
-        </is>
-      </c>
+        <v>122200697</v>
+      </c>
+      <c r="I29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>0085489004</t>
+          <t>PMP1249564</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-852931</v>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>7344450</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
       <c r="H30" s="2" t="n">
-        <v>-852931</v>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489004</t>
-        </is>
-      </c>
+        <v>7344450</v>
+      </c>
+      <c r="I30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>0085489005</t>
+          <t>PMP1249565</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1235221</v>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>75077367</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
       <c r="H31" s="2" t="n">
-        <v>-1235221</v>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489005</t>
-        </is>
-      </c>
+        <v>75077367</v>
+      </c>
+      <c r="I31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>0085489006</t>
+          <t>PMP1249566</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-2772024</v>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>15478421</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
       <c r="H32" s="2" t="n">
-        <v>-2772024</v>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489006</t>
-        </is>
-      </c>
+        <v>15478421</v>
+      </c>
+      <c r="I32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0085489007</t>
+          <t>PMP1249894</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-3198490</v>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>5509234</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
       <c r="H33" s="2" t="n">
-        <v>-3198490</v>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489007</t>
-        </is>
-      </c>
+        <v>5509234</v>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>0085489008</t>
+          <t>PMP1249897</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-4472640</v>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>11607265</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
       <c r="H34" s="2" t="n">
-        <v>-4472640</v>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489008</t>
-        </is>
-      </c>
+        <v>11607265</v>
+      </c>
+      <c r="I34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>0085489009</t>
+          <t>PMP1249898</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-4895525</v>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>3747972</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
       <c r="H35" s="2" t="n">
-        <v>-4895525</v>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489009</t>
-        </is>
-      </c>
+        <v>3747972</v>
+      </c>
+      <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>0085489010</t>
+          <t>PMP1249901</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-6266272</v>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>1322814</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
       <c r="H36" s="2" t="n">
-        <v>-6266272</v>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489010</t>
-        </is>
-      </c>
+        <v>1322814</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>0085489011</t>
+          <t>PMP1249972</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-7156225</v>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>125839982</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
       <c r="H37" s="2" t="n">
-        <v>-7156225</v>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489011</t>
-        </is>
-      </c>
+        <v>125839982</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>0085489012</t>
+          <t>PMP1249973</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-7343319</v>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>28730082</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
       <c r="H38" s="2" t="n">
-        <v>-7343319</v>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489012</t>
-        </is>
-      </c>
+        <v>28730082</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>0085489013</t>
+          <t>PMP1249974</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-16267041</v>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>3055563</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
       <c r="H39" s="2" t="n">
-        <v>-16267041</v>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489013</t>
-        </is>
-      </c>
+        <v>3055563</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>0085489014</t>
+          <t>PMP1249975</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-19679618</v>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>198843616</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
       <c r="H40" s="2" t="n">
-        <v>-19679618</v>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489014</t>
-        </is>
-      </c>
+        <v>198843616</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>0085489015</t>
+          <t>PMP1249976</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-22519415</v>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>86264216</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
       <c r="H41" s="2" t="n">
-        <v>-22519415</v>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489015</t>
-        </is>
-      </c>
+        <v>86264216</v>
+      </c>
+      <c r="I41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>0085489016</t>
+          <t>PMP1250219</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-24608350</v>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>62919991</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
       <c r="H42" s="2" t="n">
-        <v>-24608350</v>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489016</t>
-        </is>
-      </c>
+        <v>62919991</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>0085489017</t>
+          <t>PMP1250222</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-63642284</v>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>2602887</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
       <c r="H43" s="2" t="n">
-        <v>-63642284</v>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489017</t>
-        </is>
-      </c>
+        <v>2602887</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>0085489018</t>
+          <t>PMP1250223</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-77643586</v>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>39567495</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
       <c r="H44" s="2" t="n">
-        <v>-77643586</v>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489018</t>
-        </is>
-      </c>
+        <v>39567495</v>
+      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>0085489642</t>
+          <t>PMP1250224</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-38727613</v>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>10928542</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
       <c r="H45" s="2" t="n">
-        <v>-38727613</v>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>DESCUENTO 0085489642</t>
-        </is>
-      </c>
+        <v>10928542</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>4631066394</t>
+          <t>PMP1250225</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-35833</v>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>34995137</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
       <c r="H46" s="2" t="n">
-        <v>-35833</v>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>AVERIA 4631066394</t>
-        </is>
-      </c>
+        <v>34995137</v>
+      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="C47" s="6" t="inlineStr">
@@ -1417,11 +1189,11 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>4633043274</t>
+          <t>4633807051</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-107500</v>
+        <v>-7083</v>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
@@ -1434,11 +1206,11 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>-107500</v>
+        <v>-7083</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>AVERIA 4633043274</t>
+          <t>AVERIA 4633807051</t>
         </is>
       </c>
     </row>
@@ -1450,11 +1222,11 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>4633141222</t>
+          <t>4634054712</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-31860</v>
+        <v>-221909</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
@@ -1467,11 +1239,11 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>-31860</v>
+        <v>-221909</v>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>AVERIA 4633141222</t>
+          <t>AVERIA 4634054712</t>
         </is>
       </c>
     </row>
@@ -1483,28 +1255,28 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>4633373549</t>
+          <t>PMP1249400</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-29575</v>
+        <v>-220481</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>-29575</v>
+        <v>-220481</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>AVERIA 4633373549</t>
+          <t>RECHAZO PMP1249400</t>
         </is>
       </c>
     </row>
@@ -1516,28 +1288,28 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>9801649295</t>
+          <t>PMP1249558</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-817632</v>
+        <v>-96148</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>-817632</v>
+        <v>-96148</v>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649295</t>
+          <t>RECHAZO PMP1249558</t>
         </is>
       </c>
     </row>
@@ -1549,28 +1321,28 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>9801649296</t>
+          <t>PMP1249559</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-817632</v>
+        <v>-2395</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>-817632</v>
+        <v>-2395</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649296</t>
+          <t>RECHAZO PMP1249559</t>
         </is>
       </c>
     </row>
@@ -1582,28 +1354,28 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>9801649297</t>
+          <t>PMP1249563</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-3353617</v>
+        <v>-754</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-3353617</v>
+        <v>-754</v>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649297</t>
+          <t>RECHAZO PMP1249563</t>
         </is>
       </c>
     </row>
@@ -1615,28 +1387,28 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>9801649298</t>
+          <t>PMP1249565</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-13687887</v>
+        <v>-634</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-13687887</v>
+        <v>-634</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649298</t>
+          <t>RECHAZO PMP1249565</t>
         </is>
       </c>
     </row>
@@ -1648,28 +1420,28 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>9801649299</t>
+          <t>PMP1249972</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>-14589753</v>
+        <v>-289187</v>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>-14589753</v>
+        <v>-289187</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649299</t>
+          <t>RECHAZO PMP1249972</t>
         </is>
       </c>
     </row>
@@ -1681,28 +1453,28 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>9801649300</t>
+          <t>PMP1249976</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>-16674003</v>
+        <v>-909</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-16674003</v>
+        <v>-909</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649300</t>
+          <t>RECHAZO PMP1249976</t>
         </is>
       </c>
     </row>
@@ -1714,28 +1486,28 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>9801649301</t>
+          <t>PMP1250219</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>-19800379</v>
+        <v>-1597</v>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>-19800379</v>
+        <v>-1597</v>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649301</t>
+          <t>RECHAZO PMP1250219</t>
         </is>
       </c>
     </row>
@@ -1747,28 +1519,28 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>9801649302</t>
+          <t>PMP1250225</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>-21786554</v>
+        <v>-368</v>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>RECHAZO</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>-21786554</v>
+        <v>-368</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649302</t>
+          <t>RECHAZO PMP1250225</t>
         </is>
       </c>
     </row>
@@ -1780,28 +1552,28 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>9801649303</t>
+          <t>PMP1249244</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>-47451687</v>
+        <v>-1</v>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>-47451687</v>
+        <v>-1</v>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649303</t>
+          <t>MENORES VALORES PMP1249244</t>
         </is>
       </c>
     </row>
@@ -1813,28 +1585,28 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>9801649304</t>
+          <t>PMP1249400</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>-54866013</v>
+        <v>-1</v>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>-54866013</v>
+        <v>-1</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649304</t>
+          <t>MENORES VALORES PMP1249400</t>
         </is>
       </c>
     </row>
@@ -1846,28 +1618,28 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>9801649305</t>
+          <t>PMP1249557</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>-65740358</v>
+        <v>-0.1600000001490116</v>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>-65740358</v>
+        <v>-0.1600000001490116</v>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>FACT PROVEEDOR 9801649305</t>
+          <t>MENORES VALORES PMP1249557</t>
         </is>
       </c>
     </row>
@@ -1879,28 +1651,28 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>PMP1243437</t>
+          <t>PMP1249558</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-2</v>
+        <v>0.1299999952316284</v>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>-2</v>
+        <v>0.1299999952316284</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1243437</t>
+          <t>MENORES VALORES PMP1249558</t>
         </is>
       </c>
     </row>
@@ -1912,28 +1684,28 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>PMP1243438</t>
+          <t>PMP1249561</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>-143069</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>-143069</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1243438</t>
+          <t>MENORES VALORES PMP1249561</t>
         </is>
       </c>
     </row>
@@ -1945,28 +1717,28 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>PMP1243439</t>
+          <t>PMP1249562</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>-9553281</v>
+        <v>154.320000000298</v>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>-9553281</v>
+        <v>154.320000000298</v>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1243439</t>
+          <t>MENORES VALORES PMP1249562</t>
         </is>
       </c>
     </row>
@@ -1978,28 +1750,28 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>PMP1243546</t>
+          <t>PMP1249563</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>-97382</v>
+        <v>-0.8799999952316284</v>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>-97382</v>
+        <v>-0.8799999952316284</v>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1243546</t>
+          <t>MENORES VALORES PMP1249563</t>
         </is>
       </c>
     </row>
@@ -2011,28 +1783,28 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>PMP1243639</t>
+          <t>PMP1249564</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>-649</v>
+        <v>-0.599999999627471</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>RECHAZO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>-649</v>
+        <v>-0.599999999627471</v>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>RECHAZO PMP1243639</t>
+          <t>MENORES VALORES PMP1249564</t>
         </is>
       </c>
     </row>
@@ -2044,11 +1816,11 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>PMP1243434</t>
+          <t>PMP1249565</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>38.15999999642372</v>
+        <v>-0.739999994635582</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
@@ -2057,15 +1829,15 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>38.15999999642372</v>
+        <v>-0.739999994635582</v>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243434</t>
+          <t>MENORES VALORES PMP1249565</t>
         </is>
       </c>
     </row>
@@ -2077,11 +1849,11 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>PMP1243435</t>
+          <t>PMP1249566</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>-0.2399999983608723</v>
+        <v>-0.900000000372529</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
@@ -2094,11 +1866,11 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>-0.2399999983608723</v>
+        <v>-0.900000000372529</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243435</t>
+          <t>MENORES VALORES PMP1249566</t>
         </is>
       </c>
     </row>
@@ -2110,11 +1882,11 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>PMP1243437</t>
+          <t>PMP1249894</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
@@ -2127,11 +1899,11 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243437</t>
+          <t>MENORES VALORES PMP1249894</t>
         </is>
       </c>
     </row>
@@ -2143,11 +1915,11 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>PMP1243438</t>
+          <t>PMP1249897</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.2800000011920929</v>
+        <v>-1</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
@@ -2156,15 +1928,15 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.2800000011920929</v>
+        <v>-1</v>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243438</t>
+          <t>MENORES VALORES PMP1249897</t>
         </is>
       </c>
     </row>
@@ -2176,11 +1948,11 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>PMP1243439</t>
+          <t>PMP1249973</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>-0.2200000286102295</v>
+        <v>-0.9600000008940697</v>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
@@ -2193,11 +1965,11 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>-0.2200000286102295</v>
+        <v>-0.9600000008940697</v>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243439</t>
+          <t>MENORES VALORES PMP1249973</t>
         </is>
       </c>
     </row>
@@ -2209,11 +1981,11 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>PMP1243546</t>
+          <t>PMP1249975</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-1.700000002980232</v>
+        <v>246.9600000083447</v>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
@@ -2222,15 +1994,15 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>-1.700000002980232</v>
+        <v>246.9600000083447</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243546</t>
+          <t>MENORES VALORES PMP1249975</t>
         </is>
       </c>
     </row>
@@ -2242,11 +2014,11 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>PMP1243639</t>
+          <t>PMP1249976</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
@@ -2259,11 +2031,110 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>MENORES VALORES PMP1243639</t>
+          <t>MENORES VALORES PMP1249976</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>PMP1250223</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>271.9200000017881</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>271.9200000017881</v>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>MENORES VALORES PMP1250223</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>PMP1250224</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>-0.599999999627471</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>-0.599999999627471</v>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>MENORES VALORES PMP1250224</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>PMP1250225</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0.3900000005960464</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0.3900000005960464</v>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>MENORES VALORES PMP1250225</t>
         </is>
       </c>
     </row>

--- a/Template_HRC.xlsx
+++ b/Template_HRC.xlsx
@@ -612,7 +612,11 @@
       <c r="H19" s="2" t="n">
         <v>31277975</v>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="C20" s="6" t="inlineStr">
@@ -633,7 +637,11 @@
       <c r="H20" s="2" t="n">
         <v>1102345</v>
       </c>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249258</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="C21" s="6" t="inlineStr">
@@ -654,7 +662,11 @@
       <c r="H21" s="2" t="n">
         <v>27692682</v>
       </c>
-      <c r="I21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249400</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="C22" s="6" t="inlineStr">
@@ -675,7 +687,11 @@
       <c r="H22" s="2" t="n">
         <v>4992313</v>
       </c>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249405</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="C23" s="6" t="inlineStr">
@@ -696,7 +712,11 @@
       <c r="H23" s="2" t="n">
         <v>20100423</v>
       </c>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="C24" s="6" t="inlineStr">
@@ -717,7 +737,11 @@
       <c r="H24" s="2" t="n">
         <v>72307698</v>
       </c>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249558</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="C25" s="6" t="inlineStr">
@@ -738,7 +762,11 @@
       <c r="H25" s="2" t="n">
         <v>94379986</v>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249559</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="C26" s="6" t="inlineStr">
@@ -759,7 +787,11 @@
       <c r="H26" s="2" t="n">
         <v>2263380</v>
       </c>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249560</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="C27" s="6" t="inlineStr">
@@ -780,7 +812,11 @@
       <c r="H27" s="2" t="n">
         <v>79954317</v>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249561</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="C28" s="6" t="inlineStr">
@@ -801,7 +837,11 @@
       <c r="H28" s="2" t="n">
         <v>19480076</v>
       </c>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249562</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="C29" s="6" t="inlineStr">
@@ -822,7 +862,11 @@
       <c r="H29" s="2" t="n">
         <v>122200697</v>
       </c>
-      <c r="I29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249563</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="C30" s="6" t="inlineStr">
@@ -843,7 +887,11 @@
       <c r="H30" s="2" t="n">
         <v>7344450</v>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249564</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="C31" s="6" t="inlineStr">
@@ -864,7 +912,11 @@
       <c r="H31" s="2" t="n">
         <v>75077367</v>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249565</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="C32" s="6" t="inlineStr">
@@ -885,7 +937,11 @@
       <c r="H32" s="2" t="n">
         <v>15478421</v>
       </c>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249566</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="C33" s="6" t="inlineStr">
@@ -906,7 +962,11 @@
       <c r="H33" s="2" t="n">
         <v>5509234</v>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249894</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="C34" s="6" t="inlineStr">
@@ -927,7 +987,11 @@
       <c r="H34" s="2" t="n">
         <v>11607265</v>
       </c>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249897</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="C35" s="6" t="inlineStr">
@@ -948,7 +1012,11 @@
       <c r="H35" s="2" t="n">
         <v>3747972</v>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249898</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="C36" s="6" t="inlineStr">
@@ -969,7 +1037,11 @@
       <c r="H36" s="2" t="n">
         <v>1322814</v>
       </c>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249901</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="C37" s="6" t="inlineStr">
@@ -990,7 +1062,11 @@
       <c r="H37" s="2" t="n">
         <v>125839982</v>
       </c>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249972</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="C38" s="6" t="inlineStr">
@@ -1011,7 +1087,11 @@
       <c r="H38" s="2" t="n">
         <v>28730082</v>
       </c>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249973</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="C39" s="6" t="inlineStr">
@@ -1032,7 +1112,11 @@
       <c r="H39" s="2" t="n">
         <v>3055563</v>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249974</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="C40" s="6" t="inlineStr">
@@ -1053,7 +1137,11 @@
       <c r="H40" s="2" t="n">
         <v>198843616</v>
       </c>
-      <c r="I40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249975</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="C41" s="6" t="inlineStr">
@@ -1074,7 +1162,11 @@
       <c r="H41" s="2" t="n">
         <v>86264216</v>
       </c>
-      <c r="I41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1249976</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="C42" s="6" t="inlineStr">
@@ -1095,7 +1187,11 @@
       <c r="H42" s="2" t="n">
         <v>62919991</v>
       </c>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1250219</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="C43" s="6" t="inlineStr">
@@ -1116,7 +1212,11 @@
       <c r="H43" s="2" t="n">
         <v>2602887</v>
       </c>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1250222</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="C44" s="6" t="inlineStr">
@@ -1137,7 +1237,11 @@
       <c r="H44" s="2" t="n">
         <v>39567495</v>
       </c>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1250223</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="C45" s="6" t="inlineStr">
@@ -1158,7 +1262,11 @@
       <c r="H45" s="2" t="n">
         <v>10928542</v>
       </c>
-      <c r="I45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1250224</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="C46" s="6" t="inlineStr">
@@ -1179,7 +1287,11 @@
       <c r="H46" s="2" t="n">
         <v>34995137</v>
       </c>
-      <c r="I46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PMP1250225</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="C47" s="6" t="inlineStr">
